--- a/data/trans_orig/Q70-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q70-Clase-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,49</t>
+          <t>4,25</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,2</t>
+          <t>9,0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,72</t>
+          <t>6,48</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,34</t>
+          <t>0,5; 1,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 7,59</t>
+          <t>0,47; 7,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,1</t>
+          <t>0,55; 2,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,09; 7,36</t>
+          <t>2,81; 6,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 5,03</t>
+          <t>0,66; 5,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,88</t>
+          <t>0,7; 1,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,45</t>
+          <t>0,85; 4,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,32; 13,66</t>
+          <t>6,15; 12,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,29</t>
+          <t>0,68; 2,45</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 5,41</t>
+          <t>0,69; 4,77</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,7</t>
+          <t>0,81; 2,55</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,28; 9,03</t>
+          <t>4,87; 8,71</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,61</t>
+          <t>6,23</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,47</t>
+          <t>5,89</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,09</t>
+          <t>6,07</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,8</t>
+          <t>0,55; 6,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,22</t>
+          <t>0,55; 4,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,17</t>
+          <t>0,9; 7,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,28; 11,43</t>
+          <t>3,98; 10,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,05</t>
+          <t>0,82; 2,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 11,1</t>
+          <t>0,94; 10,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 5,46</t>
+          <t>1,05; 5,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,75; 7,89</t>
+          <t>3,97; 9,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,54</t>
+          <t>0,85; 3,64</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 5,28</t>
+          <t>1,04; 5,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,37; 5,41</t>
+          <t>1,36; 5,61</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,52; 8,63</t>
+          <t>4,53; 8,76</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,41</t>
+          <t>6,41</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,92</t>
+          <t>6,64</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,86</t>
+          <t>6,46</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 1,9</t>
+          <t>0,74; 1,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 4,74</t>
+          <t>0,63; 4,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,13</t>
+          <t>0,79; 3,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 8,04</t>
+          <t>3,08; 14,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,98</t>
+          <t>0,4; 1,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,23</t>
+          <t>0,21; 1,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 14,52</t>
+          <t>0,66; 17,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,45; 18,1</t>
+          <t>2,45; 15,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,7</t>
+          <t>0,75; 1,75</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,04</t>
+          <t>0,56; 3,45</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 5,16</t>
+          <t>1,07; 4,8</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,38; 8,09</t>
+          <t>3,67; 12,86</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,1</t>
+          <t>7,57</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,68</t>
+          <t>9,12</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,78</t>
+          <t>8,25</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,97</t>
+          <t>1,03; 2,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,09</t>
+          <t>0,93; 4,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 6,4</t>
+          <t>1,54; 5,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,07; 13,24</t>
+          <t>4,93; 13,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 8,75</t>
+          <t>1,1; 8,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 6,61</t>
+          <t>0,55; 7,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 6,16</t>
+          <t>0,84; 6,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,04; 13,33</t>
+          <t>6,9; 13,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,35</t>
+          <t>1,28; 3,7</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,17</t>
+          <t>0,98; 3,97</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,64</t>
+          <t>1,52; 4,63</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,74; 11,8</t>
+          <t>6,35; 11,3</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8,12</t>
+          <t>6,88</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7,9</t>
+          <t>9,99</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,98</t>
+          <t>8,45</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,19</t>
+          <t>0,73; 3,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,81</t>
+          <t>0,81; 2,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,62</t>
+          <t>0,57; 2,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,0; 14,29</t>
+          <t>4,24; 11,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,23</t>
+          <t>0,9; 6,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,94; 7,15</t>
+          <t>1,07; 7,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,65</t>
+          <t>0,51; 3,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,21; 13,06</t>
+          <t>6,55; 14,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,86</t>
+          <t>1,09; 3,77</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 5,11</t>
+          <t>1,14; 4,53</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,36</t>
+          <t>0,74; 2,55</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,19; 11,47</t>
+          <t>6,16; 11,55</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6,03</t>
+          <t>6,41</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8,24</t>
+          <t>8,54</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,97</t>
+          <t>7,34</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,05</t>
+          <t>1,04; 2,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,74</t>
+          <t>1,12; 2,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,55</t>
+          <t>1,39; 3,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,08; 7,99</t>
+          <t>5,08; 8,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,29</t>
+          <t>1,26; 3,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,77</t>
+          <t>1,14; 3,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,38</t>
+          <t>1,4; 3,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,65; 10,08</t>
+          <t>7,26; 10,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,14</t>
+          <t>1,25; 2,19</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,59</t>
+          <t>1,24; 2,6</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,96</t>
+          <t>1,51; 2,88</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,58; 8,24</t>
+          <t>6,29; 8,55</t>
         </is>
       </c>
     </row>
